--- a/armor-bench-starter/docs/Categories_v2.xlsx
+++ b/armor-bench-starter/docs/Categories_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CS-Admin\Documents\armor-benchmark-2025\armor-bench-starter\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{804A9760-5CA9-41C7-8D65-6BDCCECABFAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BAA46F1-4C7E-4857-AC37-C693E29323B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="64">
   <si>
     <t>Categories</t>
   </si>
@@ -484,6 +484,15 @@
 The derogation provisions relating to the home territory of a belligerent are not applicable
 in occupied territory, even though the occupied territory may arguably be characterized as the
 home territory of the opposing belligerent (i.e., the country being occupied).</t>
+  </si>
+  <si>
+    <t>Document</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Text</t>
   </si>
 </sst>
 </file>
@@ -850,7 +859,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" style="3" customWidth="1"/>
@@ -859,18 +868,18 @@
     <col min="4" max="16384" width="8.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
@@ -878,21 +887,21 @@
         <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="150" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
@@ -900,32 +909,32 @@
         <v>21</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="135" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="120" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="150" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>11</v>
       </c>
@@ -933,10 +942,10 @@
         <v>21</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="120" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
@@ -944,10 +953,10 @@
         <v>21</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>11</v>
       </c>
@@ -955,10 +964,10 @@
         <v>21</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>11</v>
       </c>
@@ -966,21 +975,21 @@
         <v>21</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="105" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="105" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
@@ -988,7 +997,7 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="75" x14ac:dyDescent="0.25">
@@ -999,7 +1008,7 @@
         <v>27</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="75" x14ac:dyDescent="0.25">
@@ -1010,32 +1019,32 @@
         <v>27</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="300" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>27</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="300" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>27</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>11</v>
       </c>
@@ -1043,10 +1052,10 @@
         <v>27</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="105" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>11</v>
       </c>
@@ -1054,7 +1063,7 @@
         <v>27</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="75" x14ac:dyDescent="0.25">
@@ -1065,43 +1074,43 @@
         <v>27</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+    <row r="22" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>11</v>
       </c>
@@ -1109,10 +1118,10 @@
         <v>5</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="210" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>11</v>
       </c>
@@ -1120,10 +1129,10 @@
         <v>5</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="135" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>11</v>
       </c>
@@ -1131,10 +1140,10 @@
         <v>5</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="210" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>11</v>
       </c>
@@ -1142,10 +1151,10 @@
         <v>5</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="150" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>11</v>
       </c>
@@ -1153,10 +1162,10 @@
         <v>5</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>11</v>
       </c>
@@ -1164,10 +1173,10 @@
         <v>5</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>11</v>
       </c>
@@ -1175,10 +1184,10 @@
         <v>5</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>11</v>
       </c>
@@ -1186,21 +1195,21 @@
         <v>5</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="135" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="135" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>11</v>
       </c>
@@ -1208,10 +1217,10 @@
         <v>45</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="180" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>11</v>
       </c>
@@ -1219,10 +1228,10 @@
         <v>45</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="180" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>11</v>
       </c>
@@ -1230,10 +1239,10 @@
         <v>45</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="135" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>11</v>
       </c>
@@ -1241,10 +1250,10 @@
         <v>45</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="180" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>11</v>
       </c>
@@ -1252,7 +1261,7 @@
         <v>45</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="180" x14ac:dyDescent="0.25">
@@ -1263,32 +1272,32 @@
         <v>45</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="180" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C38" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="120" x14ac:dyDescent="0.25">
+      <c r="C38" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="C39" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="120" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>11</v>
       </c>
@@ -1296,18 +1305,18 @@
         <v>45</v>
       </c>
       <c r="C40" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="90" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="90" x14ac:dyDescent="0.25">
@@ -1318,10 +1327,10 @@
         <v>8</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>11</v>
       </c>
@@ -1329,10 +1338,10 @@
         <v>8</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>11</v>
       </c>
@@ -1340,10 +1349,10 @@
         <v>8</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>11</v>
       </c>
@@ -1351,6 +1360,17 @@
         <v>8</v>
       </c>
       <c r="C45" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1367,7 +1387,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>A1:A40</xm:sqref>
+          <xm:sqref>A2:A41</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
           <x14:formula1>
@@ -1376,7 +1396,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>B1:B50</xm:sqref>
+          <xm:sqref>B2:B51</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
